--- a/doc/help_dialogs/Input_files/keyboardshortcuts.xlsx
+++ b/doc/help_dialogs/Input_files/keyboardshortcuts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Keyboard Shortcuts" sheetId="1" state="visible" r:id="rId3"/>
@@ -158,8 +158,7 @@
     <t xml:space="preserve">J</t>
   </si>
   <si>
-    <t xml:space="preserve">Toggle Playback Events
-(Expert and Standard modes)</t>
+    <t xml:space="preserve">Toggle Playback Events</t>
   </si>
   <si>
     <t xml:space="preserve">H\nCTRL+H [Win]</t>
@@ -871,52 +870,56 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1224,7 +1227,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1989,13 +1992,13 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="38.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="35.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="9" t="s">
         <v>198</v>
       </c>
     </row>
@@ -2011,222 +2014,222 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>169</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>202</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>204</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>171</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>207</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>178</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>211</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>213</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>216</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>218</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>221</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="11" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>224</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>229</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>231</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>233</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>236</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>157</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>240</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>242</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>243</v>
       </c>
     </row>
